--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Misc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260672BF-7013-4874-A939-8F4B4AEC8A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154BB628-36EE-45FE-9544-D38456F642BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5025" yWindow="1755" windowWidth="28770" windowHeight="16260" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -243,7 +243,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -280,7 +280,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,15 +646,18 @@
         <v>10000</v>
       </c>
       <c r="C2" s="10">
-        <f>A2</f>
-        <v>3.5999999999999997E-2</v>
+        <f>A3</f>
+        <v>0.1</v>
       </c>
       <c r="D2" s="11">
         <f>C2/12</f>
-        <v>2.9999999999999996E-3</v>
+        <v>8.3333333333333332E-3</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>0.1</v>
+      </c>
       <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
@@ -729,67 +731,67 @@
       </c>
       <c r="C6" s="17">
         <f>B2*(1+D2)</f>
-        <v>10029.999999999998</v>
+        <v>10083.333333333334</v>
       </c>
       <c r="D6" s="17">
         <f>B2*D2</f>
-        <v>29.999999999999996</v>
+        <v>83.333333333333329</v>
       </c>
       <c r="E6" s="18">
         <f>C6-B2</f>
-        <v>29.999999999998181</v>
+        <v>83.33333333333394</v>
       </c>
       <c r="F6" s="16">
         <v>13</v>
       </c>
       <c r="G6" s="17">
         <f>C17*(1+D2)</f>
-        <v>10397.097802289942</v>
+        <v>11139.190096699742</v>
       </c>
       <c r="H6" s="17">
         <f>C17*D2</f>
-        <v>31.097999408643894</v>
+        <v>92.059422286774719</v>
       </c>
       <c r="I6" s="18">
         <f>G6-B2</f>
-        <v>397.09780228994168</v>
-      </c>
-      <c r="J6" s="4">
+        <v>1139.1900966997418</v>
+      </c>
+      <c r="J6" s="16">
         <v>25</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="17">
         <f>G17*(1+D2)</f>
-        <v>10777.631376907515</v>
-      </c>
-      <c r="L6" s="1">
+        <v>12305.608860536884</v>
+      </c>
+      <c r="L6" s="17">
         <f>G17*D2</f>
-        <v>32.236185574000544</v>
-      </c>
-      <c r="M6" s="5">
+        <v>101.69924678129657</v>
+      </c>
+      <c r="M6" s="18">
         <f>K6-B2</f>
-        <v>777.631376907515</v>
+        <v>2305.6088605368841</v>
       </c>
       <c r="N6" s="3">
         <v>37</v>
       </c>
       <c r="O6" s="1">
         <f>K17*(1+D2)</f>
-        <v>11172.092472855062</v>
+        <v>13594.1669110565</v>
       </c>
       <c r="P6" s="1">
         <f>K17*D2</f>
-        <v>33.416029330573465</v>
+        <v>112.34848686823554</v>
       </c>
       <c r="Q6" s="5">
         <f>O6-B2</f>
-        <v>1172.0924728550617</v>
+        <v>3594.1669110564999</v>
       </c>
       <c r="S6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="T6" s="7">
         <f>O6-B2</f>
-        <v>1172.0924728550617</v>
+        <v>3594.1669110564999</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -801,56 +803,56 @@
       </c>
       <c r="C7" s="17">
         <f>C6*(1+D2)</f>
-        <v>10060.089999999997</v>
+        <v>10167.361111111111</v>
       </c>
       <c r="D7" s="17">
         <f>C6*D2</f>
-        <v>30.089999999999989</v>
+        <v>84.027777777777786</v>
       </c>
       <c r="E7" s="18">
         <f>C7-B2</f>
-        <v>60.089999999996508</v>
+        <v>167.36111111111131</v>
       </c>
       <c r="F7" s="19">
         <v>14</v>
       </c>
       <c r="G7" s="17">
         <f>G6*(1+D2)</f>
-        <v>10428.289095696811</v>
+        <v>11232.016680838906</v>
       </c>
       <c r="H7" s="17">
         <f>G6*D2</f>
-        <v>31.191293406869821</v>
+        <v>92.82658413916451</v>
       </c>
       <c r="I7" s="18">
         <f>G7-B2</f>
-        <v>428.28909569681127</v>
+        <v>1232.0166808389058</v>
       </c>
       <c r="J7" s="3">
         <v>26</v>
       </c>
       <c r="K7" s="1">
         <f>K6*(1+D2)</f>
-        <v>10809.964271038236</v>
+        <v>12408.155601041357</v>
       </c>
       <c r="L7" s="1">
         <f>K6*D2</f>
-        <v>32.332894130722543</v>
+        <v>102.54674050447403</v>
       </c>
       <c r="M7" s="5">
         <f>K7-B2</f>
-        <v>809.96427103823589</v>
-      </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
+        <v>2408.1556010413569</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
       <c r="S7" s="15" t="s">
         <v>5</v>
       </c>
       <c r="T7" s="5">
         <f>B2+T6</f>
-        <v>11172.092472855062</v>
+        <v>13594.1669110565</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -862,56 +864,56 @@
       </c>
       <c r="C8" s="17">
         <f>C7*(1+D2)</f>
-        <v>10090.270269999995</v>
+        <v>10252.08912037037</v>
       </c>
       <c r="D8" s="17">
         <f>C7*D2</f>
-        <v>30.180269999999986</v>
+        <v>84.728009259259267</v>
       </c>
       <c r="E8" s="18">
         <f>C8-B2</f>
-        <v>90.270269999995435</v>
+        <v>252.08912037037044</v>
       </c>
       <c r="F8" s="19">
         <v>15</v>
       </c>
       <c r="G8" s="17">
         <f>G7*(1+D2)</f>
-        <v>10459.573962983901</v>
+        <v>11325.616819845896</v>
       </c>
       <c r="H8" s="17">
         <f>G7*D2</f>
-        <v>31.284867287090432</v>
+        <v>93.600139006990887</v>
       </c>
       <c r="I8" s="18">
         <f>G8-B2</f>
-        <v>459.57396298390086</v>
+        <v>1325.6168198458963</v>
       </c>
       <c r="J8" s="3">
         <v>27</v>
       </c>
       <c r="K8" s="1">
         <f>K7*(1+D2)</f>
-        <v>10842.39416385135</v>
+        <v>12511.5568977167</v>
       </c>
       <c r="L8" s="1">
         <f>K7*D2</f>
-        <v>32.429892813114705</v>
+        <v>103.40129667534464</v>
       </c>
       <c r="M8" s="5">
         <f>K8-B2</f>
-        <v>842.39416385134973</v>
-      </c>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
+        <v>2511.5568977167004</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
       <c r="S8" s="15" t="s">
         <v>6</v>
       </c>
       <c r="T8" s="5">
         <f>T7-B2</f>
-        <v>1172.0924728550617</v>
+        <v>3594.1669110564999</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -923,56 +925,56 @@
       </c>
       <c r="C9" s="17">
         <f>C8*(1+D2)</f>
-        <v>10120.541080809995</v>
+        <v>10337.523196373457</v>
       </c>
       <c r="D9" s="17">
         <f>C8*D2</f>
-        <v>30.270810809999983</v>
+        <v>85.434076003086417</v>
       </c>
       <c r="E9" s="18">
         <f>C9-B2</f>
-        <v>120.54108080999504</v>
+        <v>337.52319637345681</v>
       </c>
       <c r="F9" s="19">
         <v>16</v>
       </c>
       <c r="G9" s="17">
         <f>G8*(1+D2)</f>
-        <v>10490.952684872851</v>
+        <v>11419.996960011278</v>
       </c>
       <c r="H9" s="17">
         <f>G8*D2</f>
-        <v>31.378721888951699</v>
+        <v>94.380140165382471</v>
       </c>
       <c r="I9" s="18">
         <f>G9-B2</f>
-        <v>490.95268487285102</v>
+        <v>1419.9969600112781</v>
       </c>
       <c r="J9" s="3">
         <v>28</v>
       </c>
       <c r="K9" s="1">
         <f>K8*(1+D2)</f>
-        <v>10874.921346342902</v>
+        <v>12615.81987186434</v>
       </c>
       <c r="L9" s="1">
         <f>K8*D2</f>
-        <v>32.527182491554044</v>
+        <v>104.26297414763917</v>
       </c>
       <c r="M9" s="5">
         <f>K9-B2</f>
-        <v>874.92134634290232</v>
-      </c>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
+        <v>2615.8198718643398</v>
+      </c>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
       <c r="S9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="T9" s="9">
         <f>B2-T8</f>
-        <v>8827.9075271449383</v>
+        <v>6405.8330889435001</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -984,50 +986,50 @@
       </c>
       <c r="C10" s="17">
         <f>C9*(1+D2)</f>
-        <v>10150.902704052423</v>
+        <v>10423.669223009902</v>
       </c>
       <c r="D10" s="17">
         <f>C9*D2</f>
-        <v>30.361623242429982</v>
+        <v>86.14602663644547</v>
       </c>
       <c r="E10" s="18">
         <f>C10-B2</f>
-        <v>150.90270405242336</v>
+        <v>423.66922300990154</v>
       </c>
       <c r="F10" s="19">
         <v>17</v>
       </c>
       <c r="G10" s="17">
         <f>G9*(1+D2)</f>
-        <v>10522.425542927469</v>
+        <v>11515.163601344706</v>
       </c>
       <c r="H10" s="17">
         <f>G9*D2</f>
-        <v>31.472858054618548</v>
+        <v>95.166641333427322</v>
       </c>
       <c r="I10" s="18">
         <f>G10-B2</f>
-        <v>522.425542927469</v>
+        <v>1515.163601344706</v>
       </c>
       <c r="J10" s="3">
         <v>19</v>
       </c>
       <c r="K10" s="1">
         <f>K9*(1+D2)</f>
-        <v>10907.546110381931</v>
+        <v>12720.951704129875</v>
       </c>
       <c r="L10" s="1">
         <f>K9*D2</f>
-        <v>32.624764039028705</v>
+        <v>105.13183226553616</v>
       </c>
       <c r="M10" s="5">
         <f>K10-B2</f>
-        <v>907.5461103819307</v>
-      </c>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
+        <v>2720.951704129875</v>
+      </c>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1038,50 +1040,50 @@
       </c>
       <c r="C11" s="17">
         <f>C10*(1+D2)</f>
-        <v>10181.355412164579</v>
+        <v>10510.53313320165</v>
       </c>
       <c r="D11" s="17">
         <f>C10*D2</f>
-        <v>30.452708112157268</v>
+        <v>86.863910191749184</v>
       </c>
       <c r="E11" s="18">
         <f>C11-B2</f>
-        <v>181.35541216457932</v>
+        <v>510.53313320165034</v>
       </c>
       <c r="F11" s="19">
         <v>18</v>
       </c>
       <c r="G11" s="17">
         <f>G10*(1+D2)</f>
-        <v>10553.99281955625</v>
+        <v>11611.123298022578</v>
       </c>
       <c r="H11" s="17">
         <f>G10*D2</f>
-        <v>31.567276628782402</v>
+        <v>95.959696677872543</v>
       </c>
       <c r="I11" s="18">
         <f>G11-B2</f>
-        <v>553.99281955624974</v>
+        <v>1611.1232980225777</v>
       </c>
       <c r="J11" s="3">
         <v>30</v>
       </c>
       <c r="K11" s="1">
         <f>K10*(1+D2)</f>
-        <v>10940.268748713075</v>
+        <v>12826.959634997624</v>
       </c>
       <c r="L11" s="1">
         <f>K10*D2</f>
-        <v>32.722638331145788</v>
+        <v>106.00793086774895</v>
       </c>
       <c r="M11" s="5">
         <f>K11-B2</f>
-        <v>940.26874871307518</v>
-      </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
+        <v>2826.9596349976237</v>
+      </c>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1092,50 +1094,50 @@
       </c>
       <c r="C12" s="17">
         <f>C11*(1+D2)</f>
-        <v>10211.899478401072</v>
+        <v>10598.120909311663</v>
       </c>
       <c r="D12" s="17">
         <f>C11*D2</f>
-        <v>30.544066236493734</v>
+        <v>87.587776110013749</v>
       </c>
       <c r="E12" s="18">
         <f>C12-B2</f>
-        <v>211.89947840107197</v>
+        <v>598.12090931166313</v>
       </c>
       <c r="F12" s="19">
         <v>19</v>
       </c>
       <c r="G12" s="17">
         <f>G11*(1+D2)</f>
-        <v>10585.654798014917</v>
+        <v>11707.882658839431</v>
       </c>
       <c r="H12" s="17">
         <f>G11*D2</f>
-        <v>31.661978458668745</v>
+        <v>96.759360816854809</v>
       </c>
       <c r="I12" s="18">
         <f>G12-B2</f>
-        <v>585.65479801491711</v>
+        <v>1707.8826588394313</v>
       </c>
       <c r="J12" s="3">
         <v>31</v>
       </c>
       <c r="K12" s="1">
         <f>K11*(1+D2)</f>
-        <v>10973.089554959213</v>
+        <v>12933.85096528927</v>
       </c>
       <c r="L12" s="1">
         <f>K11*D2</f>
-        <v>32.82080624613922</v>
+        <v>106.89133029164687</v>
       </c>
       <c r="M12" s="5">
         <f>K12-B2</f>
-        <v>973.08955495921327</v>
-      </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
+        <v>2933.8509652892699</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1146,50 +1148,50 @@
       </c>
       <c r="C13" s="17">
         <f>C12*(1+D2)</f>
-        <v>10242.535176836274</v>
+        <v>10686.438583555926</v>
       </c>
       <c r="D13" s="17">
         <f>C12*D2</f>
-        <v>30.635698435203214</v>
+        <v>88.317674244263856</v>
       </c>
       <c r="E13" s="18">
         <f>C13-B2</f>
-        <v>242.53517683627433</v>
+        <v>686.43858355592602</v>
       </c>
       <c r="F13" s="19">
         <v>20</v>
       </c>
       <c r="G13" s="17">
         <f>G12*(1+D2)</f>
-        <v>10617.411762408961</v>
+        <v>11805.448347663092</v>
       </c>
       <c r="H13" s="17">
         <f>G12*D2</f>
-        <v>31.756964394044747</v>
+        <v>97.56568882366193</v>
       </c>
       <c r="I13" s="18">
         <f>G13-B2</f>
-        <v>617.41176240896129</v>
+        <v>1805.4483476630921</v>
       </c>
       <c r="J13" s="3">
         <v>32</v>
       </c>
       <c r="K13" s="1">
         <f>K12*(1+D2)</f>
-        <v>11006.00882362409</v>
+        <v>13041.63305666668</v>
       </c>
       <c r="L13" s="1">
         <f>K12*D2</f>
-        <v>32.919268664877634</v>
+        <v>107.78209137741058</v>
       </c>
       <c r="M13" s="5">
         <f>K13-B2</f>
-        <v>1006.0088236240899</v>
-      </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
+        <v>3041.6330566666802</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1200,50 +1202,50 @@
       </c>
       <c r="C14" s="17">
         <f>C13*(1+D2)</f>
-        <v>10273.262782366783</v>
+        <v>10775.492238418892</v>
       </c>
       <c r="D14" s="17">
         <f>C13*D2</f>
-        <v>30.727605530508818</v>
+        <v>89.053654862966056</v>
       </c>
       <c r="E14" s="18">
         <f>C14-B2</f>
-        <v>273.26278236678263</v>
+        <v>775.49223841889216</v>
       </c>
       <c r="F14" s="19">
         <v>21</v>
       </c>
       <c r="G14" s="17">
         <f>G13*(1+D2)</f>
-        <v>10649.263997696187</v>
+        <v>11903.827083893617</v>
       </c>
       <c r="H14" s="17">
         <f>G13*D2</f>
-        <v>31.852235287226879</v>
+        <v>98.37873623052576</v>
       </c>
       <c r="I14" s="18">
         <f>G14-B2</f>
-        <v>649.26399769618729</v>
+        <v>1903.8270838936169</v>
       </c>
       <c r="J14" s="3">
         <v>33</v>
       </c>
       <c r="K14" s="1">
         <f>K13*(1+D2)</f>
-        <v>11039.026850094961</v>
+        <v>13150.313332138901</v>
       </c>
       <c r="L14" s="1">
         <f>K13*D2</f>
-        <v>33.018026470872265</v>
+        <v>108.68027547222233</v>
       </c>
       <c r="M14" s="5">
         <f>K14-B2</f>
-        <v>1039.0268500949605</v>
-      </c>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
+        <v>3150.3133321389014</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1254,50 +1256,50 @@
       </c>
       <c r="C15" s="17">
         <f>C14*(1+D2)</f>
-        <v>10304.082570713881</v>
+        <v>10865.288007072382</v>
       </c>
       <c r="D15" s="17">
         <f>C14*D2</f>
-        <v>30.819788347100346</v>
+        <v>89.795768653490768</v>
       </c>
       <c r="E15" s="18">
         <f>C15-B2</f>
-        <v>304.08257071388107</v>
+        <v>865.28800707238224</v>
       </c>
       <c r="F15" s="19">
         <v>22</v>
       </c>
       <c r="G15" s="17">
         <f>G14*(1+D2)</f>
-        <v>10681.211789689274</v>
+        <v>12003.025642926063</v>
       </c>
       <c r="H15" s="17">
         <f>G14*D2</f>
-        <v>31.947791993088558</v>
+        <v>99.198559032446809</v>
       </c>
       <c r="I15" s="18">
         <f>G15-B2</f>
-        <v>681.21178968927416</v>
+        <v>2003.0256429260626</v>
       </c>
       <c r="J15" s="3">
         <v>34</v>
       </c>
       <c r="K15" s="1">
         <f>K14*(1+D2)</f>
-        <v>11072.143930645245</v>
+        <v>13259.899276573391</v>
       </c>
       <c r="L15" s="1">
         <f>K14*D2</f>
-        <v>33.117080550284875</v>
+        <v>109.58594443449084</v>
       </c>
       <c r="M15" s="5">
         <f>K15-B2</f>
-        <v>1072.1439306452448</v>
-      </c>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
+        <v>3259.899276573391</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1308,50 +1310,50 @@
       </c>
       <c r="C16" s="17">
         <f>C15*(1+D2)</f>
-        <v>10334.994818426021</v>
+        <v>10955.832073797985</v>
       </c>
       <c r="D16" s="17">
         <f>C15*D2</f>
-        <v>30.912247712141639</v>
+        <v>90.544066725603187</v>
       </c>
       <c r="E16" s="18">
         <f>C16-B2</f>
-        <v>334.99481842602108</v>
+        <v>955.83207379798478</v>
       </c>
       <c r="F16" s="19">
         <v>23</v>
       </c>
       <c r="G16" s="17">
         <f>G15*(1+D2)</f>
-        <v>10713.255425058342</v>
+        <v>12103.050856617112</v>
       </c>
       <c r="H16" s="17">
         <f>G15*D2</f>
-        <v>32.043635369067822</v>
+        <v>100.02521369105052</v>
       </c>
       <c r="I16" s="18">
         <f>G16-B2</f>
-        <v>713.25542505834164</v>
+        <v>2103.050856617112</v>
       </c>
       <c r="J16" s="3">
         <v>35</v>
       </c>
       <c r="K16" s="1">
         <f>K15*(1+D2)</f>
-        <v>11105.360362437179</v>
+        <v>13370.398437211503</v>
       </c>
       <c r="L16" s="1">
         <f>K15*D2</f>
-        <v>33.216431791935733</v>
+        <v>110.49916063811159</v>
       </c>
       <c r="M16" s="5">
         <f>K16-B2</f>
-        <v>1105.360362437179</v>
-      </c>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
+        <v>3370.3984372115028</v>
+      </c>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1362,50 +1364,50 @@
       </c>
       <c r="C17" s="17">
         <f>C16*(1+D2)</f>
-        <v>10365.999802881299</v>
+        <v>11047.130674412967</v>
       </c>
       <c r="D17" s="17">
         <f>C16*D2</f>
-        <v>31.004984455278059</v>
+        <v>91.298600614983201</v>
       </c>
       <c r="E17" s="18">
         <f>C17-B2</f>
-        <v>365.99980288129882</v>
+        <v>1047.130674412967</v>
       </c>
       <c r="F17" s="19">
         <v>24</v>
       </c>
       <c r="G17" s="17">
         <f>G16*(1+D2)</f>
-        <v>10745.395191333515</v>
+        <v>12203.909613755588</v>
       </c>
       <c r="H17" s="17">
         <f>G16*D2</f>
-        <v>32.13976627517502</v>
+        <v>100.85875713847594</v>
       </c>
       <c r="I17" s="18">
         <f>G17-B2</f>
-        <v>745.39519133351496</v>
+        <v>2203.909613755588</v>
       </c>
       <c r="J17" s="3">
         <v>36</v>
       </c>
       <c r="K17" s="1">
         <f>K16*(1+D2)</f>
-        <v>11138.67644352449</v>
+        <v>13481.818424188265</v>
       </c>
       <c r="L17" s="1">
         <f>K16*D2</f>
-        <v>33.316081087311531</v>
+        <v>111.41998697676252</v>
       </c>
       <c r="M17" s="5">
         <f>K17-B2</f>
-        <v>1138.6764435244895</v>
-      </c>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
+        <v>3481.8184241882645</v>
+      </c>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="14"/>
@@ -1578,15 +1580,15 @@
       <c r="N23" s="3">
         <v>37</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="1">
         <f>K34*(1+D20)</f>
         <v>44688.369891420247</v>
       </c>
-      <c r="P23" s="22">
+      <c r="P23" s="1">
         <f>K34*D20</f>
         <v>133.66411732229386</v>
       </c>
-      <c r="Q23" s="22">
+      <c r="Q23" s="1">
         <f>O23-B20</f>
         <v>4688.3698914202469</v>
       </c>
@@ -1644,10 +1646,10 @@
         <f>K24-B20</f>
         <v>3239.8570841529436</v>
       </c>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="22"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
       <c r="S24" s="15" t="s">
         <v>5</v>
       </c>
@@ -1702,10 +1704,10 @@
         <f>K25-B20</f>
         <v>3369.5766554053989</v>
       </c>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
       <c r="S25" s="15" t="s">
         <v>6</v>
       </c>
@@ -1760,10 +1762,10 @@
         <f>K26-B20</f>
         <v>3499.6853853716093</v>
       </c>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
       <c r="S26" s="8" t="s">
         <v>19</v>
       </c>
@@ -1818,10 +1820,10 @@
         <f>K27-B20</f>
         <v>3630.1844415277228</v>
       </c>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
@@ -1869,10 +1871,10 @@
         <f>K28-B20</f>
         <v>3761.0749948523007</v>
       </c>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
@@ -1920,10 +1922,10 @@
         <f>K29-B20</f>
         <v>3892.3582198368531</v>
       </c>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="22"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
@@ -1971,10 +1973,10 @@
         <f>K30-B20</f>
         <v>4024.0352944963597</v>
       </c>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="22"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B31" s="3">
@@ -2022,10 +2024,10 @@
         <f>K31-B20</f>
         <v>4156.1074003798421</v>
       </c>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="22"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B32" s="3">
@@ -2073,10 +2075,10 @@
         <f>K32-B20</f>
         <v>4288.5757225809793</v>
       </c>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="3">
@@ -2124,10 +2126,10 @@
         <f>K33-B20</f>
         <v>4421.441449748716</v>
       </c>
-      <c r="N33" s="22"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="22"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="3">
@@ -2175,10 +2177,10 @@
         <f>K34-B20</f>
         <v>4554.7057740979581</v>
       </c>
-      <c r="N34" s="22"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154BB628-36EE-45FE-9544-D38456F642BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352D6AC4-0EFA-46F3-B7B0-DD0263930DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="4155" yWindow="1095" windowWidth="24360" windowHeight="16905" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352D6AC4-0EFA-46F3-B7B0-DD0263930DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74C3931-96FD-4026-BB07-05B45389BD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="1095" windowWidth="24360" windowHeight="16905" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="3615" yWindow="2010" windowWidth="27180" windowHeight="16905" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -243,7 +243,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -280,6 +280,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83046D5A-2E5B-4B8F-925A-51AAA62DB907}">
-  <dimension ref="A2:T34"/>
+  <dimension ref="A2:U34"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -636,9 +638,10 @@
     <col min="18" max="18" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>3.5999999999999997E-2</v>
       </c>
@@ -654,13 +657,13 @@
         <v>8.3333333333333332E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>0.1</v>
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="C4" s="21" t="s">
         <v>0</v>
@@ -680,7 +683,7 @@
       <c r="P4" s="20"/>
       <c r="Q4" s="20"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="12" t="s">
         <v>2</v>
@@ -722,7 +725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -794,7 +797,7 @@
         <v>3594.1669110564999</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -828,18 +831,18 @@
         <f>G7-B2</f>
         <v>1232.0166808389058</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="19">
         <v>26</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="17">
         <f>K6*(1+D2)</f>
         <v>12408.155601041357</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="17">
         <f>K6*D2</f>
         <v>102.54674050447403</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="18">
         <f>K7-B2</f>
         <v>2408.1556010413569</v>
       </c>
@@ -855,7 +858,7 @@
         <v>13594.1669110565</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -916,7 +919,7 @@
         <v>3594.1669110564999</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -977,7 +980,7 @@
         <v>6405.8330889435001</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1027,11 +1030,10 @@
         <v>2720.951704129875</v>
       </c>
       <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1085,7 +1087,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1139,7 +1141,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1192,8 +1194,9 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U13" s="22"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1249,9 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U14" s="23"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1301,7 +1305,7 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2188,5 +2192,6 @@
     <mergeCell ref="C4:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74C3931-96FD-4026-BB07-05B45389BD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA578899-2D6F-40B4-835B-650E7425C7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="2010" windowWidth="27180" windowHeight="16905" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="3495" yWindow="495" windowWidth="32970" windowHeight="18735" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -277,11 +277,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,19 +665,19 @@
     </row>
     <row r="4" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
@@ -892,18 +892,18 @@
         <f>G8-B2</f>
         <v>1325.6168198458963</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="19">
         <v>27</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="17">
         <f>K7*(1+D2)</f>
         <v>12511.5568977167</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8" s="17">
         <f>K7*D2</f>
         <v>103.40129667534464</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="18">
         <f>K8-B2</f>
         <v>2511.5568977167004</v>
       </c>
@@ -1194,7 +1194,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-      <c r="U13" s="22"/>
+      <c r="U13" s="21"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1249,7 +1249,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-      <c r="U14" s="23"/>
+      <c r="U14" s="22"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1475,19 +1475,19 @@
       </c>
     </row>
     <row r="21" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
       <c r="N21" s="20"/>
       <c r="O21" s="20"/>
       <c r="P21" s="20"/>

--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA578899-2D6F-40B4-835B-650E7425C7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8CC5B9-0516-41B3-B600-B6ABCD2574CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="495" windowWidth="32970" windowHeight="18735" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="32970" windowHeight="18735" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -649,12 +649,11 @@
         <v>10000</v>
       </c>
       <c r="C2" s="10">
-        <f>A3</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D2" s="11">
         <f>C2/12</f>
-        <v>8.3333333333333332E-3</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -734,67 +733,67 @@
       </c>
       <c r="C6" s="17">
         <f>B2*(1+D2)</f>
-        <v>10083.333333333334</v>
+        <v>10100</v>
       </c>
       <c r="D6" s="17">
         <f>B2*D2</f>
-        <v>83.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="E6" s="18">
         <f>C6-B2</f>
-        <v>83.33333333333394</v>
+        <v>100</v>
       </c>
       <c r="F6" s="16">
         <v>13</v>
       </c>
       <c r="G6" s="17">
         <f>C17*(1+D2)</f>
-        <v>11139.190096699742</v>
+        <v>11380.932804332895</v>
       </c>
       <c r="H6" s="17">
         <f>C17*D2</f>
-        <v>92.059422286774719</v>
+        <v>112.68250301319699</v>
       </c>
       <c r="I6" s="18">
         <f>G6-B2</f>
-        <v>1139.1900966997418</v>
+        <v>1380.9328043328951</v>
       </c>
       <c r="J6" s="16">
         <v>25</v>
       </c>
       <c r="K6" s="17">
         <f>G17*(1+D2)</f>
-        <v>12305.608860536884</v>
+        <v>12824.319950172341</v>
       </c>
       <c r="L6" s="17">
         <f>G17*D2</f>
-        <v>101.69924678129657</v>
+        <v>126.97346485319149</v>
       </c>
       <c r="M6" s="18">
         <f>K6-B2</f>
-        <v>2305.6088605368841</v>
+        <v>2824.3199501723411</v>
       </c>
       <c r="N6" s="3">
         <v>37</v>
       </c>
       <c r="O6" s="1">
         <f>K17*(1+D2)</f>
-        <v>13594.1669110565</v>
+        <v>14450.764714274967</v>
       </c>
       <c r="P6" s="1">
         <f>K17*D2</f>
-        <v>112.34848686823554</v>
+        <v>143.07687835915809</v>
       </c>
       <c r="Q6" s="5">
         <f>O6-B2</f>
-        <v>3594.1669110564999</v>
+        <v>4450.7647142749665</v>
       </c>
       <c r="S6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="T6" s="7">
         <f>O6-B2</f>
-        <v>3594.1669110564999</v>
+        <v>4450.7647142749665</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -806,45 +805,45 @@
       </c>
       <c r="C7" s="17">
         <f>C6*(1+D2)</f>
-        <v>10167.361111111111</v>
+        <v>10201</v>
       </c>
       <c r="D7" s="17">
         <f>C6*D2</f>
-        <v>84.027777777777786</v>
+        <v>101</v>
       </c>
       <c r="E7" s="18">
         <f>C7-B2</f>
-        <v>167.36111111111131</v>
+        <v>201</v>
       </c>
       <c r="F7" s="19">
         <v>14</v>
       </c>
       <c r="G7" s="17">
         <f>G6*(1+D2)</f>
-        <v>11232.016680838906</v>
+        <v>11494.742132376225</v>
       </c>
       <c r="H7" s="17">
         <f>G6*D2</f>
-        <v>92.82658413916451</v>
+        <v>113.80932804332895</v>
       </c>
       <c r="I7" s="18">
         <f>G7-B2</f>
-        <v>1232.0166808389058</v>
+        <v>1494.7421323762246</v>
       </c>
       <c r="J7" s="19">
         <v>26</v>
       </c>
       <c r="K7" s="17">
         <f>K6*(1+D2)</f>
-        <v>12408.155601041357</v>
+        <v>12952.563149674064</v>
       </c>
       <c r="L7" s="17">
         <f>K6*D2</f>
-        <v>102.54674050447403</v>
+        <v>128.24319950172341</v>
       </c>
       <c r="M7" s="18">
         <f>K7-B2</f>
-        <v>2408.1556010413569</v>
+        <v>2952.5631496740643</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -855,7 +854,7 @@
       </c>
       <c r="T7" s="5">
         <f>B2+T6</f>
-        <v>13594.1669110565</v>
+        <v>14450.764714274967</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -867,45 +866,45 @@
       </c>
       <c r="C8" s="17">
         <f>C7*(1+D2)</f>
-        <v>10252.08912037037</v>
+        <v>10303.01</v>
       </c>
       <c r="D8" s="17">
         <f>C7*D2</f>
-        <v>84.728009259259267</v>
+        <v>102.01</v>
       </c>
       <c r="E8" s="18">
         <f>C8-B2</f>
-        <v>252.08912037037044</v>
+        <v>303.01000000000022</v>
       </c>
       <c r="F8" s="19">
         <v>15</v>
       </c>
       <c r="G8" s="17">
         <f>G7*(1+D2)</f>
-        <v>11325.616819845896</v>
+        <v>11609.689553699987</v>
       </c>
       <c r="H8" s="17">
         <f>G7*D2</f>
-        <v>93.600139006990887</v>
+        <v>114.94742132376224</v>
       </c>
       <c r="I8" s="18">
         <f>G8-B2</f>
-        <v>1325.6168198458963</v>
+        <v>1609.6895536999873</v>
       </c>
       <c r="J8" s="19">
         <v>27</v>
       </c>
       <c r="K8" s="17">
         <f>K7*(1+D2)</f>
-        <v>12511.5568977167</v>
+        <v>13082.088781170805</v>
       </c>
       <c r="L8" s="17">
         <f>K7*D2</f>
-        <v>103.40129667534464</v>
+        <v>129.52563149674066</v>
       </c>
       <c r="M8" s="18">
         <f>K8-B2</f>
-        <v>2511.5568977167004</v>
+        <v>3082.0887811708053</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -916,7 +915,7 @@
       </c>
       <c r="T8" s="5">
         <f>T7-B2</f>
-        <v>3594.1669110564999</v>
+        <v>4450.7647142749665</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -928,45 +927,45 @@
       </c>
       <c r="C9" s="17">
         <f>C8*(1+D2)</f>
-        <v>10337.523196373457</v>
+        <v>10406.0401</v>
       </c>
       <c r="D9" s="17">
         <f>C8*D2</f>
-        <v>85.434076003086417</v>
+        <v>103.0301</v>
       </c>
       <c r="E9" s="18">
         <f>C9-B2</f>
-        <v>337.52319637345681</v>
+        <v>406.04010000000017</v>
       </c>
       <c r="F9" s="19">
         <v>16</v>
       </c>
       <c r="G9" s="17">
         <f>G8*(1+D2)</f>
-        <v>11419.996960011278</v>
+        <v>11725.786449236988</v>
       </c>
       <c r="H9" s="17">
         <f>G8*D2</f>
-        <v>94.380140165382471</v>
+        <v>116.09689553699988</v>
       </c>
       <c r="I9" s="18">
         <f>G9-B2</f>
-        <v>1419.9969600112781</v>
+        <v>1725.7864492369881</v>
       </c>
       <c r="J9" s="3">
         <v>28</v>
       </c>
       <c r="K9" s="1">
         <f>K8*(1+D2)</f>
-        <v>12615.81987186434</v>
+        <v>13212.909668982513</v>
       </c>
       <c r="L9" s="1">
         <f>K8*D2</f>
-        <v>104.26297414763917</v>
+        <v>130.82088781170805</v>
       </c>
       <c r="M9" s="5">
         <f>K9-B2</f>
-        <v>2615.8198718643398</v>
+        <v>3212.9096689825128</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -977,7 +976,7 @@
       </c>
       <c r="T9" s="9">
         <f>B2-T8</f>
-        <v>6405.8330889435001</v>
+        <v>5549.2352857250335</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -989,45 +988,45 @@
       </c>
       <c r="C10" s="17">
         <f>C9*(1+D2)</f>
-        <v>10423.669223009902</v>
+        <v>10510.100501000001</v>
       </c>
       <c r="D10" s="17">
         <f>C9*D2</f>
-        <v>86.14602663644547</v>
+        <v>104.060401</v>
       </c>
       <c r="E10" s="18">
         <f>C10-B2</f>
-        <v>423.66922300990154</v>
+        <v>510.1005010000008</v>
       </c>
       <c r="F10" s="19">
         <v>17</v>
       </c>
       <c r="G10" s="17">
         <f>G9*(1+D2)</f>
-        <v>11515.163601344706</v>
+        <v>11843.044313729359</v>
       </c>
       <c r="H10" s="17">
         <f>G9*D2</f>
-        <v>95.166641333427322</v>
+        <v>117.25786449236989</v>
       </c>
       <c r="I10" s="18">
         <f>G10-B2</f>
-        <v>1515.163601344706</v>
+        <v>1843.0443137293587</v>
       </c>
       <c r="J10" s="3">
         <v>19</v>
       </c>
       <c r="K10" s="1">
         <f>K9*(1+D2)</f>
-        <v>12720.951704129875</v>
+        <v>13345.038765672338</v>
       </c>
       <c r="L10" s="1">
         <f>K9*D2</f>
-        <v>105.13183226553616</v>
+        <v>132.12909668982513</v>
       </c>
       <c r="M10" s="5">
         <f>K10-B2</f>
-        <v>2720.951704129875</v>
+        <v>3345.0387656723378</v>
       </c>
       <c r="N10" s="1"/>
       <c r="P10" s="1"/>
@@ -1042,45 +1041,45 @@
       </c>
       <c r="C11" s="17">
         <f>C10*(1+D2)</f>
-        <v>10510.53313320165</v>
+        <v>10615.20150601</v>
       </c>
       <c r="D11" s="17">
         <f>C10*D2</f>
-        <v>86.863910191749184</v>
+        <v>105.10100501000001</v>
       </c>
       <c r="E11" s="18">
         <f>C11-B2</f>
-        <v>510.53313320165034</v>
+        <v>615.20150601000023</v>
       </c>
       <c r="F11" s="19">
         <v>18</v>
       </c>
       <c r="G11" s="17">
         <f>G10*(1+D2)</f>
-        <v>11611.123298022578</v>
+        <v>11961.474756866652</v>
       </c>
       <c r="H11" s="17">
         <f>G10*D2</f>
-        <v>95.959696677872543</v>
+        <v>118.43044313729359</v>
       </c>
       <c r="I11" s="18">
         <f>G11-B2</f>
-        <v>1611.1232980225777</v>
+        <v>1961.4747568666517</v>
       </c>
       <c r="J11" s="3">
         <v>30</v>
       </c>
       <c r="K11" s="1">
         <f>K10*(1+D2)</f>
-        <v>12826.959634997624</v>
+        <v>13478.489153329061</v>
       </c>
       <c r="L11" s="1">
         <f>K10*D2</f>
-        <v>106.00793086774895</v>
+        <v>133.45038765672339</v>
       </c>
       <c r="M11" s="5">
         <f>K11-B2</f>
-        <v>2826.9596349976237</v>
+        <v>3478.4891533290611</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1096,45 +1095,45 @@
       </c>
       <c r="C12" s="17">
         <f>C11*(1+D2)</f>
-        <v>10598.120909311663</v>
+        <v>10721.353521070101</v>
       </c>
       <c r="D12" s="17">
         <f>C11*D2</f>
-        <v>87.587776110013749</v>
+        <v>106.1520150601</v>
       </c>
       <c r="E12" s="18">
         <f>C12-B2</f>
-        <v>598.12090931166313</v>
+        <v>721.35352107010112</v>
       </c>
       <c r="F12" s="19">
         <v>19</v>
       </c>
       <c r="G12" s="17">
         <f>G11*(1+D2)</f>
-        <v>11707.882658839431</v>
+        <v>12081.089504435318</v>
       </c>
       <c r="H12" s="17">
         <f>G11*D2</f>
-        <v>96.759360816854809</v>
+        <v>119.61474756866652</v>
       </c>
       <c r="I12" s="18">
         <f>G12-B2</f>
-        <v>1707.8826588394313</v>
+        <v>2081.0895044353183</v>
       </c>
       <c r="J12" s="3">
         <v>31</v>
       </c>
       <c r="K12" s="1">
         <f>K11*(1+D2)</f>
-        <v>12933.85096528927</v>
+        <v>13613.274044862352</v>
       </c>
       <c r="L12" s="1">
         <f>K11*D2</f>
-        <v>106.89133029164687</v>
+        <v>134.78489153329062</v>
       </c>
       <c r="M12" s="5">
         <f>K12-B2</f>
-        <v>2933.8509652892699</v>
+        <v>3613.2740448623517</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1150,45 +1149,45 @@
       </c>
       <c r="C13" s="17">
         <f>C12*(1+D2)</f>
-        <v>10686.438583555926</v>
+        <v>10828.567056280803</v>
       </c>
       <c r="D13" s="17">
         <f>C12*D2</f>
-        <v>88.317674244263856</v>
+        <v>107.21353521070101</v>
       </c>
       <c r="E13" s="18">
         <f>C13-B2</f>
-        <v>686.43858355592602</v>
+        <v>828.56705628080272</v>
       </c>
       <c r="F13" s="19">
         <v>20</v>
       </c>
       <c r="G13" s="17">
         <f>G12*(1+D2)</f>
-        <v>11805.448347663092</v>
+        <v>12201.900399479671</v>
       </c>
       <c r="H13" s="17">
         <f>G12*D2</f>
-        <v>97.56568882366193</v>
+        <v>120.81089504435319</v>
       </c>
       <c r="I13" s="18">
         <f>G13-B2</f>
-        <v>1805.4483476630921</v>
+        <v>2201.9003994796713</v>
       </c>
       <c r="J13" s="3">
         <v>32</v>
       </c>
       <c r="K13" s="1">
         <f>K12*(1+D2)</f>
-        <v>13041.63305666668</v>
+        <v>13749.406785310975</v>
       </c>
       <c r="L13" s="1">
         <f>K12*D2</f>
-        <v>107.78209137741058</v>
+        <v>136.13274044862351</v>
       </c>
       <c r="M13" s="5">
         <f>K13-B2</f>
-        <v>3041.6330566666802</v>
+        <v>3749.4067853109755</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1205,45 +1204,45 @@
       </c>
       <c r="C14" s="17">
         <f>C13*(1+D2)</f>
-        <v>10775.492238418892</v>
+        <v>10936.85272684361</v>
       </c>
       <c r="D14" s="17">
         <f>C13*D2</f>
-        <v>89.053654862966056</v>
+        <v>108.28567056280804</v>
       </c>
       <c r="E14" s="18">
         <f>C14-B2</f>
-        <v>775.49223841889216</v>
+        <v>936.85272684361007</v>
       </c>
       <c r="F14" s="19">
         <v>21</v>
       </c>
       <c r="G14" s="17">
         <f>G13*(1+D2)</f>
-        <v>11903.827083893617</v>
+        <v>12323.919403474469</v>
       </c>
       <c r="H14" s="17">
         <f>G13*D2</f>
-        <v>98.37873623052576</v>
+        <v>122.01900399479672</v>
       </c>
       <c r="I14" s="18">
         <f>G14-B2</f>
-        <v>1903.8270838936169</v>
+        <v>2323.9194034744687</v>
       </c>
       <c r="J14" s="3">
         <v>33</v>
       </c>
       <c r="K14" s="1">
         <f>K13*(1+D2)</f>
-        <v>13150.313332138901</v>
+        <v>13886.900853164085</v>
       </c>
       <c r="L14" s="1">
         <f>K13*D2</f>
-        <v>108.68027547222233</v>
+        <v>137.49406785310975</v>
       </c>
       <c r="M14" s="5">
         <f>K14-B2</f>
-        <v>3150.3133321389014</v>
+        <v>3886.9008531640848</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1260,45 +1259,45 @@
       </c>
       <c r="C15" s="17">
         <f>C14*(1+D2)</f>
-        <v>10865.288007072382</v>
+        <v>11046.221254112046</v>
       </c>
       <c r="D15" s="17">
         <f>C14*D2</f>
-        <v>89.795768653490768</v>
+        <v>109.3685272684361</v>
       </c>
       <c r="E15" s="18">
         <f>C15-B2</f>
-        <v>865.28800707238224</v>
+        <v>1046.2212541120462</v>
       </c>
       <c r="F15" s="19">
         <v>22</v>
       </c>
       <c r="G15" s="17">
         <f>G14*(1+D2)</f>
-        <v>12003.025642926063</v>
+        <v>12447.158597509213</v>
       </c>
       <c r="H15" s="17">
         <f>G14*D2</f>
-        <v>99.198559032446809</v>
+        <v>123.23919403474468</v>
       </c>
       <c r="I15" s="18">
         <f>G15-B2</f>
-        <v>2003.0256429260626</v>
+        <v>2447.158597509213</v>
       </c>
       <c r="J15" s="3">
         <v>34</v>
       </c>
       <c r="K15" s="1">
         <f>K14*(1+D2)</f>
-        <v>13259.899276573391</v>
+        <v>14025.769861695726</v>
       </c>
       <c r="L15" s="1">
         <f>K14*D2</f>
-        <v>109.58594443449084</v>
+        <v>138.86900853164084</v>
       </c>
       <c r="M15" s="5">
         <f>K15-B2</f>
-        <v>3259.899276573391</v>
+        <v>4025.7698616957259</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1314,45 +1313,45 @@
       </c>
       <c r="C16" s="17">
         <f>C15*(1+D2)</f>
-        <v>10955.832073797985</v>
+        <v>11156.683466653167</v>
       </c>
       <c r="D16" s="17">
         <f>C15*D2</f>
-        <v>90.544066725603187</v>
+        <v>110.46221254112046</v>
       </c>
       <c r="E16" s="18">
         <f>C16-B2</f>
-        <v>955.83207379798478</v>
+        <v>1156.6834666531668</v>
       </c>
       <c r="F16" s="19">
         <v>23</v>
       </c>
       <c r="G16" s="17">
         <f>G15*(1+D2)</f>
-        <v>12103.050856617112</v>
+        <v>12571.630183484305</v>
       </c>
       <c r="H16" s="17">
         <f>G15*D2</f>
-        <v>100.02521369105052</v>
+        <v>124.47158597509214</v>
       </c>
       <c r="I16" s="18">
         <f>G16-B2</f>
-        <v>2103.050856617112</v>
+        <v>2571.6301834843052</v>
       </c>
       <c r="J16" s="3">
         <v>35</v>
       </c>
       <c r="K16" s="1">
         <f>K15*(1+D2)</f>
-        <v>13370.398437211503</v>
+        <v>14166.027560312683</v>
       </c>
       <c r="L16" s="1">
         <f>K15*D2</f>
-        <v>110.49916063811159</v>
+        <v>140.25769861695727</v>
       </c>
       <c r="M16" s="5">
         <f>K16-B2</f>
-        <v>3370.3984372115028</v>
+        <v>4166.0275603126829</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1368,45 +1367,45 @@
       </c>
       <c r="C17" s="17">
         <f>C16*(1+D2)</f>
-        <v>11047.130674412967</v>
+        <v>11268.250301319698</v>
       </c>
       <c r="D17" s="17">
         <f>C16*D2</f>
-        <v>91.298600614983201</v>
+        <v>111.56683466653168</v>
       </c>
       <c r="E17" s="18">
         <f>C17-B2</f>
-        <v>1047.130674412967</v>
+        <v>1268.2503013196983</v>
       </c>
       <c r="F17" s="19">
         <v>24</v>
       </c>
       <c r="G17" s="17">
         <f>G16*(1+D2)</f>
-        <v>12203.909613755588</v>
+        <v>12697.346485319149</v>
       </c>
       <c r="H17" s="17">
         <f>G16*D2</f>
-        <v>100.85875713847594</v>
+        <v>125.71630183484305</v>
       </c>
       <c r="I17" s="18">
         <f>G17-B2</f>
-        <v>2203.909613755588</v>
+        <v>2697.346485319149</v>
       </c>
       <c r="J17" s="3">
         <v>36</v>
       </c>
       <c r="K17" s="1">
         <f>K16*(1+D2)</f>
-        <v>13481.818424188265</v>
+        <v>14307.687835915809</v>
       </c>
       <c r="L17" s="1">
         <f>K16*D2</f>
-        <v>111.41998697676252</v>
+        <v>141.66027560312682</v>
       </c>
       <c r="M17" s="5">
         <f>K17-B2</f>
-        <v>3481.8184241882645</v>
+        <v>4307.687835915809</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>

--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8CC5B9-0516-41B3-B600-B6ABCD2574CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA104B0-A5E7-4808-9265-F69752662CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="32970" windowHeight="18735" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="4320" yWindow="0" windowWidth="28800" windowHeight="20985" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -952,18 +952,18 @@
         <f>G9-B2</f>
         <v>1725.7864492369881</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="19">
         <v>28</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="17">
         <f>K8*(1+D2)</f>
         <v>13212.909668982513</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="17">
         <f>K8*D2</f>
         <v>130.82088781170805</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="18">
         <f>K9-B2</f>
         <v>3212.9096689825128</v>
       </c>
@@ -1013,18 +1013,18 @@
         <f>G10-B2</f>
         <v>1843.0443137293587</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="19">
         <v>19</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="17">
         <f>K9*(1+D2)</f>
         <v>13345.038765672338</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="17">
         <f>K9*D2</f>
         <v>132.12909668982513</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="18">
         <f>K10-B2</f>
         <v>3345.0387656723378</v>
       </c>

--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA104B0-A5E7-4808-9265-F69752662CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3126A6F1-9047-4CEE-8960-B513A78A34E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="0" windowWidth="28800" windowHeight="20985" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="4200" yWindow="0" windowWidth="29010" windowHeight="20985" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1066,18 +1066,18 @@
         <f>G11-B2</f>
         <v>1961.4747568666517</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="19">
         <v>30</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="17">
         <f>K10*(1+D2)</f>
         <v>13478.489153329061</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="17">
         <f>K10*D2</f>
         <v>133.45038765672339</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="18">
         <f>K11-B2</f>
         <v>3478.4891533290611</v>
       </c>

--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3126A6F1-9047-4CEE-8960-B513A78A34E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75D7B2E-07E7-4EA4-95D8-DFA68C9743E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="0" windowWidth="29010" windowHeight="20985" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="39810" yWindow="0" windowWidth="35595" windowHeight="21705" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,8 +144,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,6 +163,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -243,7 +263,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -266,14 +286,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -281,6 +293,40 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -643,16 +689,13 @@
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
-        <v>3.5999999999999997E-2</v>
+        <v>4.3900000000000002E-2</v>
       </c>
       <c r="B2" s="1">
         <v>10000</v>
       </c>
-      <c r="C2" s="10">
-        <v>0.12</v>
-      </c>
-      <c r="D2" s="11">
-        <f>C2/12</f>
+      <c r="C2" s="11">
+        <f>A4/12</f>
         <v>0.01</v>
       </c>
     </row>
@@ -663,24 +706,26 @@
       <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="C4" s="23" t="s">
+      <c r="A4" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
@@ -725,123 +770,123 @@
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="21">
         <v>1</v>
       </c>
-      <c r="C6" s="17">
-        <f>B2*(1+D2)</f>
+      <c r="C6" s="22">
+        <f>B2*(1+C2)</f>
         <v>10100</v>
       </c>
-      <c r="D6" s="17">
-        <f>B2*D2</f>
+      <c r="D6" s="22">
+        <f>B2*C2</f>
         <v>100</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="23">
         <f>C6-B2</f>
         <v>100</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="21">
         <v>13</v>
       </c>
-      <c r="G6" s="17">
-        <f>C17*(1+D2)</f>
+      <c r="G6" s="22">
+        <f>C17*(1+C2)</f>
         <v>11380.932804332895</v>
       </c>
-      <c r="H6" s="17">
-        <f>C17*D2</f>
+      <c r="H6" s="22">
+        <f>C17*C2</f>
         <v>112.68250301319699</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="23">
         <f>G6-B2</f>
         <v>1380.9328043328951</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="21">
         <v>25</v>
       </c>
-      <c r="K6" s="17">
-        <f>G17*(1+D2)</f>
+      <c r="K6" s="22">
+        <f>G17*(1+C2)</f>
         <v>12824.319950172341</v>
       </c>
-      <c r="L6" s="17">
-        <f>G17*D2</f>
+      <c r="L6" s="22">
+        <f>G17*C2</f>
         <v>126.97346485319149</v>
       </c>
-      <c r="M6" s="18">
+      <c r="M6" s="23">
         <f>K6-B2</f>
         <v>2824.3199501723411</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="33">
         <v>37</v>
       </c>
-      <c r="O6" s="1">
-        <f>K17*(1+D2)</f>
+      <c r="O6" s="34">
+        <f>K17*(1+C2)</f>
         <v>14450.764714274967</v>
       </c>
-      <c r="P6" s="1">
-        <f>K17*D2</f>
+      <c r="P6" s="34">
+        <f>K17*C2</f>
         <v>143.07687835915809</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="35">
         <f>O6-B2</f>
         <v>4450.7647142749665</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="S6" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="37">
         <f>O6-B2</f>
         <v>4450.7647142749665</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="25">
         <v>2</v>
       </c>
-      <c r="C7" s="17">
-        <f>C6*(1+D2)</f>
+      <c r="C7" s="26">
+        <f>C6*(1+C2)</f>
         <v>10201</v>
       </c>
-      <c r="D7" s="17">
-        <f>C6*D2</f>
+      <c r="D7" s="26">
+        <f>C6*C2</f>
         <v>101</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="27">
         <f>C7-B2</f>
         <v>201</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="25">
         <v>14</v>
       </c>
-      <c r="G7" s="17">
-        <f>G6*(1+D2)</f>
+      <c r="G7" s="26">
+        <f>G6*(1+C2)</f>
         <v>11494.742132376225</v>
       </c>
-      <c r="H7" s="17">
-        <f>G6*D2</f>
+      <c r="H7" s="26">
+        <f>G6*C2</f>
         <v>113.80932804332895</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="27">
         <f>G7-B2</f>
         <v>1494.7421323762246</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="25">
         <v>26</v>
       </c>
-      <c r="K7" s="17">
-        <f>K6*(1+D2)</f>
+      <c r="K7" s="26">
+        <f>K6*(1+C2)</f>
         <v>12952.563149674064</v>
       </c>
-      <c r="L7" s="17">
-        <f>K6*D2</f>
+      <c r="L7" s="26">
+        <f>K6*C2</f>
         <v>128.24319950172341</v>
       </c>
-      <c r="M7" s="18">
+      <c r="M7" s="27">
         <f>K7-B2</f>
         <v>2952.5631496740643</v>
       </c>
@@ -849,60 +894,60 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-      <c r="S7" s="15" t="s">
+      <c r="S7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="29">
         <f>B2+T6</f>
         <v>14450.764714274967</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="21">
         <v>3</v>
       </c>
-      <c r="C8" s="17">
-        <f>C7*(1+D2)</f>
+      <c r="C8" s="22">
+        <f>C7*(1+C2)</f>
         <v>10303.01</v>
       </c>
-      <c r="D8" s="17">
-        <f>C7*D2</f>
+      <c r="D8" s="22">
+        <f>C7*C2</f>
         <v>102.01</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="23">
         <f>C8-B2</f>
         <v>303.01000000000022</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="21">
         <v>15</v>
       </c>
-      <c r="G8" s="17">
-        <f>G7*(1+D2)</f>
+      <c r="G8" s="22">
+        <f>G7*(1+C2)</f>
         <v>11609.689553699987</v>
       </c>
-      <c r="H8" s="17">
-        <f>G7*D2</f>
+      <c r="H8" s="22">
+        <f>G7*C2</f>
         <v>114.94742132376224</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="23">
         <f>G8-B2</f>
         <v>1609.6895536999873</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="21">
         <v>27</v>
       </c>
-      <c r="K8" s="17">
-        <f>K7*(1+D2)</f>
+      <c r="K8" s="22">
+        <f>K7*(1+C2)</f>
         <v>13082.088781170805</v>
       </c>
-      <c r="L8" s="17">
-        <f>K7*D2</f>
+      <c r="L8" s="22">
+        <f>K7*C2</f>
         <v>129.52563149674066</v>
       </c>
-      <c r="M8" s="18">
+      <c r="M8" s="23">
         <f>K8-B2</f>
         <v>3082.0887811708053</v>
       </c>
@@ -910,60 +955,60 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-      <c r="S8" s="15" t="s">
+      <c r="S8" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="T8" s="5">
+      <c r="T8" s="28">
         <f>T7-B2</f>
         <v>4450.7647142749665</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="25">
         <v>4</v>
       </c>
-      <c r="C9" s="17">
-        <f>C8*(1+D2)</f>
+      <c r="C9" s="26">
+        <f>C8*(1+C2)</f>
         <v>10406.0401</v>
       </c>
-      <c r="D9" s="17">
-        <f>C8*D2</f>
+      <c r="D9" s="26">
+        <f>C8*C2</f>
         <v>103.0301</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="27">
         <f>C9-B2</f>
         <v>406.04010000000017</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="25">
         <v>16</v>
       </c>
-      <c r="G9" s="17">
-        <f>G8*(1+D2)</f>
+      <c r="G9" s="26">
+        <f>G8*(1+C2)</f>
         <v>11725.786449236988</v>
       </c>
-      <c r="H9" s="17">
-        <f>G8*D2</f>
+      <c r="H9" s="26">
+        <f>G8*C2</f>
         <v>116.09689553699988</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="27">
         <f>G9-B2</f>
         <v>1725.7864492369881</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="25">
         <v>28</v>
       </c>
-      <c r="K9" s="17">
-        <f>K8*(1+D2)</f>
+      <c r="K9" s="26">
+        <f>K8*(1+C2)</f>
         <v>13212.909668982513</v>
       </c>
-      <c r="L9" s="17">
-        <f>K8*D2</f>
+      <c r="L9" s="26">
+        <f>K8*C2</f>
         <v>130.82088781170805</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="27">
         <f>K9-B2</f>
         <v>3212.9096689825128</v>
       </c>
@@ -971,60 +1016,60 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="S9" s="8" t="s">
+      <c r="S9" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="T9" s="9">
+      <c r="T9" s="40">
         <f>B2-T8</f>
         <v>5549.2352857250335</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="21">
         <v>5</v>
       </c>
-      <c r="C10" s="17">
-        <f>C9*(1+D2)</f>
+      <c r="C10" s="22">
+        <f>C9*(1+C2)</f>
         <v>10510.100501000001</v>
       </c>
-      <c r="D10" s="17">
-        <f>C9*D2</f>
+      <c r="D10" s="22">
+        <f>C9*C2</f>
         <v>104.060401</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="23">
         <f>C10-B2</f>
         <v>510.1005010000008</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="21">
         <v>17</v>
       </c>
-      <c r="G10" s="17">
-        <f>G9*(1+D2)</f>
+      <c r="G10" s="22">
+        <f>G9*(1+C2)</f>
         <v>11843.044313729359</v>
       </c>
-      <c r="H10" s="17">
-        <f>G9*D2</f>
+      <c r="H10" s="22">
+        <f>G9*C2</f>
         <v>117.25786449236989</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="23">
         <f>G10-B2</f>
         <v>1843.0443137293587</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="21">
         <v>19</v>
       </c>
-      <c r="K10" s="17">
-        <f>K9*(1+D2)</f>
+      <c r="K10" s="22">
+        <f>K9*(1+C2)</f>
         <v>13345.038765672338</v>
       </c>
-      <c r="L10" s="17">
-        <f>K9*D2</f>
+      <c r="L10" s="22">
+        <f>K9*C2</f>
         <v>132.12909668982513</v>
       </c>
-      <c r="M10" s="18">
+      <c r="M10" s="23">
         <f>K10-B2</f>
         <v>3345.0387656723378</v>
       </c>
@@ -1033,51 +1078,51 @@
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="25">
         <v>6</v>
       </c>
-      <c r="C11" s="17">
-        <f>C10*(1+D2)</f>
+      <c r="C11" s="26">
+        <f>C10*(1+C2)</f>
         <v>10615.20150601</v>
       </c>
-      <c r="D11" s="17">
-        <f>C10*D2</f>
+      <c r="D11" s="26">
+        <f>C10*C2</f>
         <v>105.10100501000001</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="27">
         <f>C11-B2</f>
         <v>615.20150601000023</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="25">
         <v>18</v>
       </c>
-      <c r="G11" s="17">
-        <f>G10*(1+D2)</f>
+      <c r="G11" s="26">
+        <f>G10*(1+C2)</f>
         <v>11961.474756866652</v>
       </c>
-      <c r="H11" s="17">
-        <f>G10*D2</f>
+      <c r="H11" s="26">
+        <f>G10*C2</f>
         <v>118.43044313729359</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="27">
         <f>G11-B2</f>
         <v>1961.4747568666517</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="25">
         <v>30</v>
       </c>
-      <c r="K11" s="17">
-        <f>K10*(1+D2)</f>
+      <c r="K11" s="26">
+        <f>K10*(1+C2)</f>
         <v>13478.489153329061</v>
       </c>
-      <c r="L11" s="17">
-        <f>K10*D2</f>
+      <c r="L11" s="26">
+        <f>K10*C2</f>
         <v>133.45038765672339</v>
       </c>
-      <c r="M11" s="18">
+      <c r="M11" s="27">
         <f>K11-B2</f>
         <v>3478.4891533290611</v>
       </c>
@@ -1087,51 +1132,51 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="21">
         <v>7</v>
       </c>
-      <c r="C12" s="17">
-        <f>C11*(1+D2)</f>
+      <c r="C12" s="22">
+        <f>C11*(1+C2)</f>
         <v>10721.353521070101</v>
       </c>
-      <c r="D12" s="17">
-        <f>C11*D2</f>
+      <c r="D12" s="22">
+        <f>C11*C2</f>
         <v>106.1520150601</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="23">
         <f>C12-B2</f>
         <v>721.35352107010112</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="21">
         <v>19</v>
       </c>
-      <c r="G12" s="17">
-        <f>G11*(1+D2)</f>
+      <c r="G12" s="22">
+        <f>G11*(1+C2)</f>
         <v>12081.089504435318</v>
       </c>
-      <c r="H12" s="17">
-        <f>G11*D2</f>
+      <c r="H12" s="22">
+        <f>G11*C2</f>
         <v>119.61474756866652</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="23">
         <f>G12-B2</f>
         <v>2081.0895044353183</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="21">
         <v>31</v>
       </c>
-      <c r="K12" s="1">
-        <f>K11*(1+D2)</f>
+      <c r="K12" s="22">
+        <f>K11*(1+C2)</f>
         <v>13613.274044862352</v>
       </c>
-      <c r="L12" s="1">
-        <f>K11*D2</f>
+      <c r="L12" s="22">
+        <f>K11*C2</f>
         <v>134.78489153329062</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="23">
         <f>K12-B2</f>
         <v>3613.2740448623517</v>
       </c>
@@ -1141,51 +1186,51 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="25">
         <v>8</v>
       </c>
-      <c r="C13" s="17">
-        <f>C12*(1+D2)</f>
+      <c r="C13" s="26">
+        <f>C12*(1+C2)</f>
         <v>10828.567056280803</v>
       </c>
-      <c r="D13" s="17">
-        <f>C12*D2</f>
+      <c r="D13" s="26">
+        <f>C12*C2</f>
         <v>107.21353521070101</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="27">
         <f>C13-B2</f>
         <v>828.56705628080272</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="25">
         <v>20</v>
       </c>
-      <c r="G13" s="17">
-        <f>G12*(1+D2)</f>
+      <c r="G13" s="26">
+        <f>G12*(1+C2)</f>
         <v>12201.900399479671</v>
       </c>
-      <c r="H13" s="17">
-        <f>G12*D2</f>
+      <c r="H13" s="26">
+        <f>G12*C2</f>
         <v>120.81089504435319</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="27">
         <f>G13-B2</f>
         <v>2201.9003994796713</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="30">
         <v>32</v>
       </c>
-      <c r="K13" s="1">
-        <f>K12*(1+D2)</f>
+      <c r="K13" s="31">
+        <f>K12*(1+C2)</f>
         <v>13749.406785310975</v>
       </c>
-      <c r="L13" s="1">
-        <f>K12*D2</f>
+      <c r="L13" s="31">
+        <f>K12*C2</f>
         <v>136.13274044862351</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M13" s="32">
         <f>K13-B2</f>
         <v>3749.4067853109755</v>
       </c>
@@ -1193,54 +1238,54 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-      <c r="U13" s="21"/>
+      <c r="U13" s="17"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="21">
         <v>9</v>
       </c>
-      <c r="C14" s="17">
-        <f>C13*(1+D2)</f>
+      <c r="C14" s="22">
+        <f>C13*(1+C2)</f>
         <v>10936.85272684361</v>
       </c>
-      <c r="D14" s="17">
-        <f>C13*D2</f>
+      <c r="D14" s="22">
+        <f>C13*C2</f>
         <v>108.28567056280804</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="23">
         <f>C14-B2</f>
         <v>936.85272684361007</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="21">
         <v>21</v>
       </c>
-      <c r="G14" s="17">
-        <f>G13*(1+D2)</f>
+      <c r="G14" s="22">
+        <f>G13*(1+C2)</f>
         <v>12323.919403474469</v>
       </c>
-      <c r="H14" s="17">
-        <f>G13*D2</f>
+      <c r="H14" s="22">
+        <f>G13*C2</f>
         <v>122.01900399479672</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="23">
         <f>G14-B2</f>
         <v>2323.9194034744687</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="33">
         <v>33</v>
       </c>
-      <c r="K14" s="1">
-        <f>K13*(1+D2)</f>
+      <c r="K14" s="34">
+        <f>K13*(1+C2)</f>
         <v>13886.900853164085</v>
       </c>
-      <c r="L14" s="1">
-        <f>K13*D2</f>
+      <c r="L14" s="34">
+        <f>K13*C2</f>
         <v>137.49406785310975</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="35">
         <f>K14-B2</f>
         <v>3886.9008531640848</v>
       </c>
@@ -1248,54 +1293,54 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-      <c r="U14" s="22"/>
+      <c r="U14" s="18"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="25">
         <v>10</v>
       </c>
-      <c r="C15" s="17">
-        <f>C14*(1+D2)</f>
+      <c r="C15" s="26">
+        <f>C14*(1+C2)</f>
         <v>11046.221254112046</v>
       </c>
-      <c r="D15" s="17">
-        <f>C14*D2</f>
+      <c r="D15" s="26">
+        <f>C14*C2</f>
         <v>109.3685272684361</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="27">
         <f>C15-B2</f>
         <v>1046.2212541120462</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="25">
         <v>22</v>
       </c>
-      <c r="G15" s="17">
-        <f>G14*(1+D2)</f>
+      <c r="G15" s="26">
+        <f>G14*(1+C2)</f>
         <v>12447.158597509213</v>
       </c>
-      <c r="H15" s="17">
-        <f>G14*D2</f>
+      <c r="H15" s="26">
+        <f>G14*C2</f>
         <v>123.23919403474468</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="27">
         <f>G15-B2</f>
         <v>2447.158597509213</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="30">
         <v>34</v>
       </c>
-      <c r="K15" s="1">
-        <f>K14*(1+D2)</f>
+      <c r="K15" s="31">
+        <f>K14*(1+C2)</f>
         <v>14025.769861695726</v>
       </c>
-      <c r="L15" s="1">
-        <f>K14*D2</f>
+      <c r="L15" s="31">
+        <f>K14*C2</f>
         <v>138.86900853164084</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="32">
         <f>K15-B2</f>
         <v>4025.7698616957259</v>
       </c>
@@ -1305,51 +1350,51 @@
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="21">
         <v>11</v>
       </c>
-      <c r="C16" s="17">
-        <f>C15*(1+D2)</f>
+      <c r="C16" s="22">
+        <f>C15*(1+C2)</f>
         <v>11156.683466653167</v>
       </c>
-      <c r="D16" s="17">
-        <f>C15*D2</f>
+      <c r="D16" s="22">
+        <f>C15*C2</f>
         <v>110.46221254112046</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="23">
         <f>C16-B2</f>
         <v>1156.6834666531668</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="21">
         <v>23</v>
       </c>
-      <c r="G16" s="17">
-        <f>G15*(1+D2)</f>
+      <c r="G16" s="22">
+        <f>G15*(1+C2)</f>
         <v>12571.630183484305</v>
       </c>
-      <c r="H16" s="17">
-        <f>G15*D2</f>
+      <c r="H16" s="22">
+        <f>G15*C2</f>
         <v>124.47158597509214</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="23">
         <f>G16-B2</f>
         <v>2571.6301834843052</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="33">
         <v>35</v>
       </c>
-      <c r="K16" s="1">
-        <f>K15*(1+D2)</f>
+      <c r="K16" s="34">
+        <f>K15*(1+C2)</f>
         <v>14166.027560312683</v>
       </c>
-      <c r="L16" s="1">
-        <f>K15*D2</f>
+      <c r="L16" s="34">
+        <f>K15*C2</f>
         <v>140.25769861695727</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="35">
         <f>K16-B2</f>
         <v>4166.0275603126829</v>
       </c>
@@ -1359,51 +1404,51 @@
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="25">
         <v>12</v>
       </c>
-      <c r="C17" s="17">
-        <f>C16*(1+D2)</f>
+      <c r="C17" s="26">
+        <f>C16*(1+C2)</f>
         <v>11268.250301319698</v>
       </c>
-      <c r="D17" s="17">
-        <f>C16*D2</f>
+      <c r="D17" s="26">
+        <f>C16*C2</f>
         <v>111.56683466653168</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="27">
         <f>C17-B2</f>
         <v>1268.2503013196983</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="25">
         <v>24</v>
       </c>
-      <c r="G17" s="17">
-        <f>G16*(1+D2)</f>
+      <c r="G17" s="26">
+        <f>G16*(1+C2)</f>
         <v>12697.346485319149</v>
       </c>
-      <c r="H17" s="17">
-        <f>G16*D2</f>
+      <c r="H17" s="26">
+        <f>G16*C2</f>
         <v>125.71630183484305</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="27">
         <f>G17-B2</f>
         <v>2697.346485319149</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="30">
         <v>36</v>
       </c>
-      <c r="K17" s="1">
-        <f>K16*(1+D2)</f>
+      <c r="K17" s="31">
+        <f>K16*(1+C2)</f>
         <v>14307.687835915809</v>
       </c>
-      <c r="L17" s="1">
-        <f>K16*D2</f>
+      <c r="L17" s="31">
+        <f>K16*C2</f>
         <v>141.66027560312682</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="32">
         <f>K17-B2</f>
         <v>4307.687835915809</v>
       </c>
@@ -1459,38 +1504,38 @@
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <f>A2</f>
-        <v>3.5999999999999997E-2</v>
+        <v>4.3900000000000002E-2</v>
       </c>
       <c r="B20" s="1">
         <v>40000</v>
       </c>
       <c r="C20" s="10">
         <f>A20</f>
-        <v>3.5999999999999997E-2</v>
+        <v>4.3900000000000002E-2</v>
       </c>
       <c r="D20" s="11">
         <f>C20/12</f>
-        <v>2.9999999999999996E-3</v>
+        <v>3.6583333333333333E-3</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
@@ -1540,67 +1585,67 @@
       </c>
       <c r="C23" s="1">
         <f>B20*(1+D20)</f>
-        <v>40119.999999999993</v>
+        <v>40146.333333333336</v>
       </c>
       <c r="D23" s="1">
         <f>B20*D20</f>
-        <v>119.99999999999999</v>
+        <v>146.33333333333334</v>
       </c>
       <c r="E23" s="5">
         <f>C23-B20</f>
-        <v>119.99999999999272</v>
+        <v>146.33333333333576</v>
       </c>
       <c r="F23" s="4">
         <v>13</v>
       </c>
       <c r="G23" s="1">
         <f>C34*(1+D20)</f>
-        <v>41588.391209159767</v>
+        <v>41944.654819851363</v>
       </c>
       <c r="H23" s="1">
         <f>C34*D20</f>
-        <v>124.39199763457557</v>
+        <v>152.88821283732636</v>
       </c>
       <c r="I23" s="5">
         <f>G23-B20</f>
-        <v>1588.3912091597667</v>
+        <v>1944.6548198513628</v>
       </c>
       <c r="J23" s="4">
         <v>25</v>
       </c>
       <c r="K23" s="1">
         <f>G34*(1+D20)</f>
-        <v>43110.52550763006</v>
+        <v>43823.530616074873</v>
       </c>
       <c r="L23" s="1">
         <f>G34*D20</f>
-        <v>128.94474229600218</v>
+        <v>159.73671269652579</v>
       </c>
       <c r="M23" s="5">
         <f>K23-B20</f>
-        <v>3110.52550763006</v>
+        <v>3823.5306160748733</v>
       </c>
       <c r="N23" s="3">
         <v>37</v>
       </c>
       <c r="O23" s="1">
         <f>K34*(1+D20)</f>
-        <v>44688.369891420247</v>
+        <v>45786.569085058371</v>
       </c>
       <c r="P23" s="1">
         <f>K34*D20</f>
-        <v>133.66411732229386</v>
+        <v>166.89198538962151</v>
       </c>
       <c r="Q23" s="1">
         <f>O23-B20</f>
-        <v>4688.3698914202469</v>
+        <v>5786.5690850583705</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>1</v>
       </c>
       <c r="T23" s="7">
         <f>O23-B20</f>
-        <v>4688.3698914202469</v>
+        <v>5786.5690850583705</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -1609,45 +1654,45 @@
       </c>
       <c r="C24" s="1">
         <f>C23*(1+D20)</f>
-        <v>40240.359999999986</v>
+        <v>40293.202002777776</v>
       </c>
       <c r="D24" s="1">
         <f>C23*D20</f>
-        <v>120.35999999999996</v>
+        <v>146.86866944444446</v>
       </c>
       <c r="E24" s="5">
         <f>C24-B20</f>
-        <v>240.35999999998603</v>
+        <v>293.20200277777622</v>
       </c>
       <c r="F24" s="3">
         <v>14</v>
       </c>
       <c r="G24" s="1">
         <f>G23*(1+D20)</f>
-        <v>41713.156382787245</v>
+        <v>42098.102348733984</v>
       </c>
       <c r="H24" s="1">
         <f>G23*D20</f>
-        <v>124.76517362747929</v>
+        <v>153.44752888262289</v>
       </c>
       <c r="I24" s="5">
         <f>G24-B20</f>
-        <v>1713.1563827872451</v>
+        <v>2098.1023487339844</v>
       </c>
       <c r="J24" s="3">
         <v>26</v>
       </c>
       <c r="K24" s="1">
         <f>K23*(1+D20)</f>
-        <v>43239.857084152944</v>
+        <v>43983.851698912011</v>
       </c>
       <c r="L24" s="1">
         <f>K23*D20</f>
-        <v>129.33157652289017</v>
+        <v>160.32108283714058</v>
       </c>
       <c r="M24" s="5">
         <f>K24-B20</f>
-        <v>3239.8570841529436</v>
+        <v>3983.8516989120108</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -1658,7 +1703,7 @@
       </c>
       <c r="T24" s="5">
         <f>B20+T23</f>
-        <v>44688.369891420247</v>
+        <v>45786.569085058371</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -1667,45 +1712,45 @@
       </c>
       <c r="C25" s="1">
         <f>C24*(1+D20)</f>
-        <v>40361.081079999982</v>
+        <v>40440.607966771269</v>
       </c>
       <c r="D25" s="1">
         <f>C24*D20</f>
-        <v>120.72107999999994</v>
+        <v>147.40596399349536</v>
       </c>
       <c r="E25" s="5">
         <f>C25-B20</f>
-        <v>361.08107999998174</v>
+        <v>440.60796677126928</v>
       </c>
       <c r="F25" s="3">
         <v>15</v>
       </c>
       <c r="G25" s="1">
         <f>G24*(1+D20)</f>
-        <v>41838.295851935603</v>
+        <v>42252.111239826438</v>
       </c>
       <c r="H25" s="1">
         <f>G24*D20</f>
-        <v>125.13946914836173</v>
+        <v>154.00889109245182</v>
       </c>
       <c r="I25" s="5">
         <f>G25-B20</f>
-        <v>1838.2958519356034</v>
+        <v>2252.1112398264377</v>
       </c>
       <c r="J25" s="3">
         <v>27</v>
       </c>
       <c r="K25" s="1">
         <f>K24*(1+D20)</f>
-        <v>43369.576655405399</v>
+        <v>44144.759289710528</v>
       </c>
       <c r="L25" s="1">
         <f>K24*D20</f>
-        <v>129.71957125245882</v>
+        <v>160.90759079851978</v>
       </c>
       <c r="M25" s="5">
         <f>K25-B20</f>
-        <v>3369.5766554053989</v>
+        <v>4144.7592897105278</v>
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -1716,7 +1761,7 @@
       </c>
       <c r="T25" s="5">
         <f>T24-B20</f>
-        <v>4688.3698914202469</v>
+        <v>5786.5690850583705</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -1725,45 +1770,45 @@
       </c>
       <c r="C26" s="1">
         <f>C25*(1+D20)</f>
-        <v>40482.16432323998</v>
+        <v>40588.553190916376</v>
       </c>
       <c r="D26" s="1">
         <f>C25*D20</f>
-        <v>121.08324323999993</v>
+        <v>147.9452241451049</v>
       </c>
       <c r="E26" s="5">
         <f>C26-B20</f>
-        <v>482.16432323998015</v>
+        <v>588.55319091637648</v>
       </c>
       <c r="F26" s="3">
         <v>16</v>
       </c>
       <c r="G26" s="1">
         <f>G25*(1+D20)</f>
-        <v>41963.810739491404</v>
+        <v>42406.683546778804</v>
       </c>
       <c r="H26" s="1">
         <f>G25*D20</f>
-        <v>125.51488755580679</v>
+        <v>154.57230695236504</v>
       </c>
       <c r="I26" s="5">
         <f>G26-B20</f>
-        <v>1963.8107394914041</v>
+        <v>2406.6835467788042</v>
       </c>
       <c r="J26" s="3">
         <v>28</v>
       </c>
       <c r="K26" s="1">
         <f>K25*(1+D20)</f>
-        <v>43499.685385371609</v>
+        <v>44306.255534112053</v>
       </c>
       <c r="L26" s="1">
         <f>K25*D20</f>
-        <v>130.10872996621617</v>
+        <v>161.49624440152434</v>
       </c>
       <c r="M26" s="5">
         <f>K26-B20</f>
-        <v>3499.6853853716093</v>
+        <v>4306.2555341120533</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -1774,7 +1819,7 @@
       </c>
       <c r="T26" s="9">
         <f>B20-T23</f>
-        <v>35311.630108579753</v>
+        <v>34213.430914941629</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -1783,45 +1828,45 @@
       </c>
       <c r="C27" s="1">
         <f>C26*(1+D20)</f>
-        <v>40603.610816209693</v>
+        <v>40737.039648006481</v>
       </c>
       <c r="D27" s="1">
         <f>C26*D20</f>
-        <v>121.44649296971993</v>
+        <v>148.48645709010242</v>
       </c>
       <c r="E27" s="5">
         <f>C27-B20</f>
-        <v>603.61081620969344</v>
+        <v>737.039648006481</v>
       </c>
       <c r="F27" s="3">
         <v>17</v>
       </c>
       <c r="G27" s="1">
         <f>G26*(1+D20)</f>
-        <v>42089.702171709876</v>
+        <v>42561.821330754101</v>
       </c>
       <c r="H27" s="1">
         <f>G26*D20</f>
-        <v>125.89143221847419</v>
+        <v>155.13778397529913</v>
       </c>
       <c r="I27" s="5">
         <f>G27-B20</f>
-        <v>2089.702171709876</v>
+        <v>2561.8213307541009</v>
       </c>
       <c r="J27" s="3">
         <v>19</v>
       </c>
       <c r="K27" s="1">
         <f>K26*(1+D20)</f>
-        <v>43630.184441527723</v>
+        <v>44468.342585607679</v>
       </c>
       <c r="L27" s="1">
         <f>K26*D20</f>
-        <v>130.49905615611482</v>
+        <v>162.08705149562658</v>
       </c>
       <c r="M27" s="5">
         <f>K27-B20</f>
-        <v>3630.1844415277228</v>
+        <v>4468.3425856076792</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -1834,45 +1879,45 @@
       </c>
       <c r="C28" s="1">
         <f>C27*(1+D20)</f>
-        <v>40725.421648658317</v>
+        <v>40886.069318052105</v>
       </c>
       <c r="D28" s="1">
         <f>C27*D20</f>
-        <v>121.81083244862907</v>
+        <v>149.0296700456237</v>
       </c>
       <c r="E28" s="5">
         <f>C28-B20</f>
-        <v>725.42164865831728</v>
+        <v>886.06931805210479</v>
       </c>
       <c r="F28" s="3">
         <v>18</v>
       </c>
       <c r="G28" s="1">
         <f>G27*(1+D20)</f>
-        <v>42215.971278224999</v>
+        <v>42717.526660455776</v>
       </c>
       <c r="H28" s="1">
         <f>G27*D20</f>
-        <v>126.26910651512961</v>
+        <v>155.70532970167542</v>
       </c>
       <c r="I28" s="5">
         <f>G28-B20</f>
-        <v>2215.971278224999</v>
+        <v>2717.5266604557764</v>
       </c>
       <c r="J28" s="3">
         <v>30</v>
       </c>
       <c r="K28" s="1">
         <f>K27*(1+D20)</f>
-        <v>43761.074994852301</v>
+        <v>44631.022605566694</v>
       </c>
       <c r="L28" s="1">
         <f>K27*D20</f>
-        <v>130.89055332458315</v>
+        <v>162.68001995901477</v>
       </c>
       <c r="M28" s="5">
         <f>K28-B20</f>
-        <v>3761.0749948523007</v>
+        <v>4631.0226055666935</v>
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -1885,45 +1930,45 @@
       </c>
       <c r="C29" s="1">
         <f>C28*(1+D20)</f>
-        <v>40847.597913604288</v>
+        <v>41035.644188307313</v>
       </c>
       <c r="D29" s="1">
         <f>C28*D20</f>
-        <v>122.17626494597494</v>
+        <v>149.57487025520729</v>
       </c>
       <c r="E29" s="5">
         <f>C29-B20</f>
-        <v>847.5979136042879</v>
+        <v>1035.644188307313</v>
       </c>
       <c r="F29" s="3">
         <v>19</v>
       </c>
       <c r="G29" s="1">
         <f>G28*(1+D20)</f>
-        <v>42342.619192059668</v>
+        <v>42873.801612155279</v>
       </c>
       <c r="H29" s="1">
         <f>G28*D20</f>
-        <v>126.64791383467498</v>
+        <v>156.27495169950072</v>
       </c>
       <c r="I29" s="5">
         <f>G29-B20</f>
-        <v>2342.6191920596684</v>
+        <v>2873.8016121552791</v>
       </c>
       <c r="J29" s="3">
         <v>31</v>
       </c>
       <c r="K29" s="1">
         <f>K28*(1+D20)</f>
-        <v>43892.358219836853</v>
+        <v>44794.297763265393</v>
       </c>
       <c r="L29" s="1">
         <f>K28*D20</f>
-        <v>131.28322498455688</v>
+        <v>163.27515769869817</v>
       </c>
       <c r="M29" s="5">
         <f>K29-B20</f>
-        <v>3892.3582198368531</v>
+        <v>4794.2977632653929</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
@@ -1936,45 +1981,45 @@
       </c>
       <c r="C30" s="1">
         <f>C29*(1+D20)</f>
-        <v>40970.140707345097</v>
+        <v>41185.766253296206</v>
       </c>
       <c r="D30" s="1">
         <f>C29*D20</f>
-        <v>122.54279374081285</v>
+        <v>150.12206498889091</v>
       </c>
       <c r="E30" s="5">
         <f>C30-B20</f>
-        <v>970.14070734509733</v>
+        <v>1185.7662532962058</v>
       </c>
       <c r="F30" s="3">
         <v>20</v>
       </c>
       <c r="G30" s="1">
         <f>G29*(1+D20)</f>
-        <v>42469.647049635845</v>
+        <v>43030.64826971975</v>
       </c>
       <c r="H30" s="1">
         <f>G29*D20</f>
-        <v>127.02785757617899</v>
+        <v>156.84665756446807</v>
       </c>
       <c r="I30" s="5">
         <f>G30-B20</f>
-        <v>2469.6470496358452</v>
+        <v>3030.6482697197498</v>
       </c>
       <c r="J30" s="3">
         <v>32</v>
       </c>
       <c r="K30" s="1">
         <f>K29*(1+D20)</f>
-        <v>44024.03529449636</v>
+        <v>44958.170235916004</v>
       </c>
       <c r="L30" s="1">
         <f>K29*D20</f>
-        <v>131.67707465951054</v>
+        <v>163.87247265061256</v>
       </c>
       <c r="M30" s="5">
         <f>K30-B20</f>
-        <v>4024.0352944963597</v>
+        <v>4958.1702359160045</v>
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -1987,45 +2032,45 @@
       </c>
       <c r="C31" s="1">
         <f>C30*(1+D20)</f>
-        <v>41093.051129467131</v>
+        <v>41336.437514839512</v>
       </c>
       <c r="D31" s="1">
         <f>C30*D20</f>
-        <v>122.91042212203527</v>
+        <v>150.67126154330862</v>
       </c>
       <c r="E31" s="5">
         <f>C31-B20</f>
-        <v>1093.0511294671305</v>
+        <v>1336.437514839512</v>
       </c>
       <c r="F31" s="3">
         <v>21</v>
       </c>
       <c r="G31" s="1">
         <f>G30*(1+D20)</f>
-        <v>42597.055990784749</v>
+        <v>43188.068724639808</v>
       </c>
       <c r="H31" s="1">
         <f>G30*D20</f>
-        <v>127.40894114890752</v>
+        <v>157.42045492005809</v>
       </c>
       <c r="I31" s="5">
         <f>G31-B20</f>
-        <v>2597.0559907847492</v>
+        <v>3188.0687246398084</v>
       </c>
       <c r="J31" s="3">
         <v>33</v>
       </c>
       <c r="K31" s="1">
         <f>K30*(1+D20)</f>
-        <v>44156.107400379842</v>
+        <v>45122.642208695732</v>
       </c>
       <c r="L31" s="1">
         <f>K30*D20</f>
-        <v>132.07210588348906</v>
+        <v>164.47197277972606</v>
       </c>
       <c r="M31" s="5">
         <f>K31-B20</f>
-        <v>4156.1074003798421</v>
+        <v>5122.6422086957318</v>
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -2038,45 +2083,45 @@
       </c>
       <c r="C32" s="1">
         <f>C31*(1+D20)</f>
-        <v>41216.330282855524</v>
+        <v>41487.659982081299</v>
       </c>
       <c r="D32" s="1">
         <f>C31*D20</f>
-        <v>123.27915338840138</v>
+        <v>151.22246724178788</v>
       </c>
       <c r="E32" s="5">
         <f>C32-B20</f>
-        <v>1216.3302828555243</v>
+        <v>1487.6599820812989</v>
       </c>
       <c r="F32" s="3">
         <v>22</v>
       </c>
       <c r="G32" s="1">
         <f>G31*(1+D20)</f>
-        <v>42724.847158757097</v>
+        <v>43346.06507605745</v>
       </c>
       <c r="H32" s="1">
         <f>G31*D20</f>
-        <v>127.79116797235423</v>
+        <v>157.99635141764062</v>
       </c>
       <c r="I32" s="5">
         <f>G32-B20</f>
-        <v>2724.8471587570966</v>
+        <v>3346.0650760574499</v>
       </c>
       <c r="J32" s="3">
         <v>34</v>
       </c>
       <c r="K32" s="1">
         <f>K31*(1+D20)</f>
-        <v>44288.575722580979</v>
+        <v>45287.715874775873</v>
       </c>
       <c r="L32" s="1">
         <f>K31*D20</f>
-        <v>132.4683222011395</v>
+        <v>165.07366608014522</v>
       </c>
       <c r="M32" s="5">
         <f>K32-B20</f>
-        <v>4288.5757225809793</v>
+        <v>5287.7158747758731</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
@@ -2089,45 +2134,45 @@
       </c>
       <c r="C33" s="1">
         <f>C32*(1+D20)</f>
-        <v>41339.979273704084</v>
+        <v>41639.435671515748</v>
       </c>
       <c r="D33" s="1">
         <f>C32*D20</f>
-        <v>123.64899084856656</v>
+        <v>151.77568943444743</v>
       </c>
       <c r="E33" s="5">
         <f>C33-B20</f>
-        <v>1339.9792737040843</v>
+        <v>1639.4356715157483</v>
       </c>
       <c r="F33" s="3">
         <v>23</v>
       </c>
       <c r="G33" s="1">
         <f>G32*(1+D20)</f>
-        <v>42853.021700233367</v>
+        <v>43504.639430794028</v>
       </c>
       <c r="H33" s="1">
         <f>G32*D20</f>
-        <v>128.17454147627129</v>
+        <v>158.57435473657685</v>
       </c>
       <c r="I33" s="5">
         <f>G33-B20</f>
-        <v>2853.0217002333666</v>
+        <v>3504.6394307940282</v>
       </c>
       <c r="J33" s="3">
         <v>35</v>
       </c>
       <c r="K33" s="1">
         <f>K32*(1+D20)</f>
-        <v>44421.441449748716</v>
+        <v>45453.393435351092</v>
       </c>
       <c r="L33" s="1">
         <f>K32*D20</f>
-        <v>132.86572716774293</v>
+        <v>165.67756057522175</v>
       </c>
       <c r="M33" s="5">
         <f>K33-B20</f>
-        <v>4421.441449748716</v>
+        <v>5453.3934353510922</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -2140,45 +2185,45 @@
       </c>
       <c r="C34" s="1">
         <f>C33*(1+D20)</f>
-        <v>41463.999211525195</v>
+        <v>41791.76660701404</v>
       </c>
       <c r="D34" s="1">
         <f>C33*D20</f>
-        <v>124.01993782111224</v>
+        <v>152.3309354982951</v>
       </c>
       <c r="E34" s="5">
         <f>C34-B20</f>
-        <v>1463.9992115251953</v>
+        <v>1791.7666070140403</v>
       </c>
       <c r="F34" s="3">
         <v>24</v>
       </c>
       <c r="G34" s="1">
         <f>G33*(1+D20)</f>
-        <v>42981.58076533406</v>
+        <v>43663.793903378348</v>
       </c>
       <c r="H34" s="1">
         <f>G33*D20</f>
-        <v>128.55906510070008</v>
+        <v>159.1544725843215</v>
       </c>
       <c r="I34" s="5">
         <f>G34-B20</f>
-        <v>2981.5807653340598</v>
+        <v>3663.7939033783477</v>
       </c>
       <c r="J34" s="3">
         <v>36</v>
       </c>
       <c r="K34" s="1">
         <f>K33*(1+D20)</f>
-        <v>44554.705774097958</v>
+        <v>45619.677099668748</v>
       </c>
       <c r="L34" s="1">
         <f>K33*D20</f>
-        <v>133.26432434924612</v>
+        <v>166.2836643176594</v>
       </c>
       <c r="M34" s="5">
         <f>K34-B20</f>
-        <v>4554.7057740979581</v>
+        <v>5619.6770996687483</v>
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>

--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75D7B2E-07E7-4EA4-95D8-DFA68C9743E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008F7A4B-86B6-4F9C-8BD1-AD4E6EE749B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39810" yWindow="0" windowWidth="35595" windowHeight="21705" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="4170" yWindow="1380" windowWidth="28800" windowHeight="15345" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -291,9 +291,6 @@
     </xf>
     <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -327,6 +324,9 @@
     <xf numFmtId="8" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -709,19 +709,19 @@
       <c r="A4" s="10">
         <v>0.12</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
       <c r="N4" s="16"/>
       <c r="O4" s="16"/>
       <c r="P4" s="16"/>
@@ -770,123 +770,123 @@
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <v>1</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="21">
         <f>B2*(1+C2)</f>
         <v>10100</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <f>B2*C2</f>
         <v>100</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <f>C6-B2</f>
         <v>100</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>13</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="21">
         <f>C17*(1+C2)</f>
         <v>11380.932804332895</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <f>C17*C2</f>
         <v>112.68250301319699</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="22">
         <f>G6-B2</f>
         <v>1380.9328043328951</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="20">
         <v>25</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="21">
         <f>G17*(1+C2)</f>
         <v>12824.319950172341</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="21">
         <f>G17*C2</f>
         <v>126.97346485319149</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="22">
         <f>K6-B2</f>
         <v>2824.3199501723411</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="32">
         <v>37</v>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="33">
         <f>K17*(1+C2)</f>
         <v>14450.764714274967</v>
       </c>
-      <c r="P6" s="34">
+      <c r="P6" s="33">
         <f>K17*C2</f>
         <v>143.07687835915809</v>
       </c>
-      <c r="Q6" s="35">
+      <c r="Q6" s="34">
         <f>O6-B2</f>
         <v>4450.7647142749665</v>
       </c>
-      <c r="S6" s="36" t="s">
+      <c r="S6" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="T6" s="37">
+      <c r="T6" s="36">
         <f>O6-B2</f>
         <v>4450.7647142749665</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="24">
         <v>2</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <f>C6*(1+C2)</f>
         <v>10201</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="25">
         <f>C6*C2</f>
         <v>101</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="26">
         <f>C7-B2</f>
         <v>201</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="24">
         <v>14</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="25">
         <f>G6*(1+C2)</f>
         <v>11494.742132376225</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="25">
         <f>G6*C2</f>
         <v>113.80932804332895</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="26">
         <f>G7-B2</f>
         <v>1494.7421323762246</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="24">
         <v>26</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="25">
         <f>K6*(1+C2)</f>
         <v>12952.563149674064</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="25">
         <f>K6*C2</f>
         <v>128.24319950172341</v>
       </c>
-      <c r="M7" s="27">
+      <c r="M7" s="26">
         <f>K7-B2</f>
         <v>2952.5631496740643</v>
       </c>
@@ -894,60 +894,60 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-      <c r="S7" s="38" t="s">
+      <c r="S7" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="T7" s="29">
+      <c r="T7" s="28">
         <f>B2+T6</f>
         <v>14450.764714274967</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <v>3</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="21">
         <f>C7*(1+C2)</f>
         <v>10303.01</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <f>C7*C2</f>
         <v>102.01</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <f>C8-B2</f>
         <v>303.01000000000022</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <v>15</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <f>G7*(1+C2)</f>
         <v>11609.689553699987</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <f>G7*C2</f>
         <v>114.94742132376224</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="22">
         <f>G8-B2</f>
         <v>1609.6895536999873</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="20">
         <v>27</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="21">
         <f>K7*(1+C2)</f>
         <v>13082.088781170805</v>
       </c>
-      <c r="L8" s="22">
+      <c r="L8" s="21">
         <f>K7*C2</f>
         <v>129.52563149674066</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="22">
         <f>K8-B2</f>
         <v>3082.0887811708053</v>
       </c>
@@ -955,60 +955,60 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-      <c r="S8" s="41" t="s">
+      <c r="S8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="27">
         <f>T7-B2</f>
         <v>4450.7647142749665</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="24">
         <v>4</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <f>C8*(1+C2)</f>
         <v>10406.0401</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="25">
         <f>C8*C2</f>
         <v>103.0301</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="26">
         <f>C9-B2</f>
         <v>406.04010000000017</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="24">
         <v>16</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="25">
         <f>G8*(1+C2)</f>
         <v>11725.786449236988</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="25">
         <f>G8*C2</f>
         <v>116.09689553699988</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="26">
         <f>G9-B2</f>
         <v>1725.7864492369881</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="24">
         <v>28</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="25">
         <f>K8*(1+C2)</f>
         <v>13212.909668982513</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="25">
         <f>K8*C2</f>
         <v>130.82088781170805</v>
       </c>
-      <c r="M9" s="27">
+      <c r="M9" s="26">
         <f>K9-B2</f>
         <v>3212.9096689825128</v>
       </c>
@@ -1016,60 +1016,60 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="S9" s="39" t="s">
+      <c r="S9" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="T9" s="40">
+      <c r="T9" s="39">
         <f>B2-T8</f>
         <v>5549.2352857250335</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <v>5</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="21">
         <f>C9*(1+C2)</f>
         <v>10510.100501000001</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <f>C9*C2</f>
         <v>104.060401</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <f>C10-B2</f>
         <v>510.1005010000008</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <v>17</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="21">
         <f>G9*(1+C2)</f>
         <v>11843.044313729359</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <f>G9*C2</f>
         <v>117.25786449236989</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="22">
         <f>G10-B2</f>
         <v>1843.0443137293587</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="20">
         <v>19</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="21">
         <f>K9*(1+C2)</f>
         <v>13345.038765672338</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="21">
         <f>K9*C2</f>
         <v>132.12909668982513</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="22">
         <f>K10-B2</f>
         <v>3345.0387656723378</v>
       </c>
@@ -1078,51 +1078,51 @@
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="24">
         <v>6</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="25">
         <f>C10*(1+C2)</f>
         <v>10615.20150601</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="25">
         <f>C10*C2</f>
         <v>105.10100501000001</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="26">
         <f>C11-B2</f>
         <v>615.20150601000023</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="24">
         <v>18</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="25">
         <f>G10*(1+C2)</f>
         <v>11961.474756866652</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="25">
         <f>G10*C2</f>
         <v>118.43044313729359</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="26">
         <f>G11-B2</f>
         <v>1961.4747568666517</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="24">
         <v>30</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="25">
         <f>K10*(1+C2)</f>
         <v>13478.489153329061</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="25">
         <f>K10*C2</f>
         <v>133.45038765672339</v>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="26">
         <f>K11-B2</f>
         <v>3478.4891533290611</v>
       </c>
@@ -1132,51 +1132,51 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <v>7</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="21">
         <f>C11*(1+C2)</f>
         <v>10721.353521070101</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <f>C11*C2</f>
         <v>106.1520150601</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="22">
         <f>C12-B2</f>
         <v>721.35352107010112</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <v>19</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="21">
         <f>G11*(1+C2)</f>
         <v>12081.089504435318</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <f>G11*C2</f>
         <v>119.61474756866652</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <f>G12-B2</f>
         <v>2081.0895044353183</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="20">
         <v>31</v>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="21">
         <f>K11*(1+C2)</f>
         <v>13613.274044862352</v>
       </c>
-      <c r="L12" s="22">
+      <c r="L12" s="21">
         <f>K11*C2</f>
         <v>134.78489153329062</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="22">
         <f>K12-B2</f>
         <v>3613.2740448623517</v>
       </c>
@@ -1186,51 +1186,51 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="24">
         <v>8</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="25">
         <f>C12*(1+C2)</f>
         <v>10828.567056280803</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="25">
         <f>C12*C2</f>
         <v>107.21353521070101</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="26">
         <f>C13-B2</f>
         <v>828.56705628080272</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <v>20</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="25">
         <f>G12*(1+C2)</f>
         <v>12201.900399479671</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="25">
         <f>G12*C2</f>
         <v>120.81089504435319</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="26">
         <f>G13-B2</f>
         <v>2201.9003994796713</v>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="29">
         <v>32</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="30">
         <f>K12*(1+C2)</f>
         <v>13749.406785310975</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="30">
         <f>K12*C2</f>
         <v>136.13274044862351</v>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="31">
         <f>K13-B2</f>
         <v>3749.4067853109755</v>
       </c>
@@ -1241,51 +1241,51 @@
       <c r="U13" s="17"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>9</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <f>C13*(1+C2)</f>
         <v>10936.85272684361</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <f>C13*C2</f>
         <v>108.28567056280804</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="22">
         <f>C14-B2</f>
         <v>936.85272684361007</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <v>21</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <f>G13*(1+C2)</f>
         <v>12323.919403474469</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <f>G13*C2</f>
         <v>122.01900399479672</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <f>G14-B2</f>
         <v>2323.9194034744687</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="32">
         <v>33</v>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="33">
         <f>K13*(1+C2)</f>
         <v>13886.900853164085</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="33">
         <f>K13*C2</f>
         <v>137.49406785310975</v>
       </c>
-      <c r="M14" s="35">
+      <c r="M14" s="34">
         <f>K14-B2</f>
         <v>3886.9008531640848</v>
       </c>
@@ -1296,51 +1296,51 @@
       <c r="U14" s="18"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="24">
         <v>10</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="25">
         <f>C14*(1+C2)</f>
         <v>11046.221254112046</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <f>C14*C2</f>
         <v>109.3685272684361</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="26">
         <f>C15-B2</f>
         <v>1046.2212541120462</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <v>22</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="25">
         <f>G14*(1+C2)</f>
         <v>12447.158597509213</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="25">
         <f>G14*C2</f>
         <v>123.23919403474468</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="26">
         <f>G15-B2</f>
         <v>2447.158597509213</v>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="29">
         <v>34</v>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="30">
         <f>K14*(1+C2)</f>
         <v>14025.769861695726</v>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="30">
         <f>K14*C2</f>
         <v>138.86900853164084</v>
       </c>
-      <c r="M15" s="32">
+      <c r="M15" s="31">
         <f>K15-B2</f>
         <v>4025.7698616957259</v>
       </c>
@@ -1350,51 +1350,51 @@
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>11</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="21">
         <f>C15*(1+C2)</f>
         <v>11156.683466653167</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <f>C15*C2</f>
         <v>110.46221254112046</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="22">
         <f>C16-B2</f>
         <v>1156.6834666531668</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <v>23</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <f>G15*(1+C2)</f>
         <v>12571.630183484305</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <f>G15*C2</f>
         <v>124.47158597509214</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <f>G16-B2</f>
         <v>2571.6301834843052</v>
       </c>
-      <c r="J16" s="33">
+      <c r="J16" s="32">
         <v>35</v>
       </c>
-      <c r="K16" s="34">
+      <c r="K16" s="33">
         <f>K15*(1+C2)</f>
         <v>14166.027560312683</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="33">
         <f>K15*C2</f>
         <v>140.25769861695727</v>
       </c>
-      <c r="M16" s="35">
+      <c r="M16" s="34">
         <f>K16-B2</f>
         <v>4166.0275603126829</v>
       </c>
@@ -1404,51 +1404,51 @@
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="24">
         <v>12</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <f>C16*(1+C2)</f>
         <v>11268.250301319698</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <f>C16*C2</f>
         <v>111.56683466653168</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="26">
         <f>C17-B2</f>
         <v>1268.2503013196983</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>24</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <f>G16*(1+C2)</f>
         <v>12697.346485319149</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <f>G16*C2</f>
         <v>125.71630183484305</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="26">
         <f>G17-B2</f>
         <v>2697.346485319149</v>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="29">
         <v>36</v>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="30">
         <f>K16*(1+C2)</f>
         <v>14307.687835915809</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="30">
         <f>K16*C2</f>
         <v>141.66027560312682</v>
       </c>
-      <c r="M17" s="32">
+      <c r="M17" s="31">
         <f>K17-B2</f>
         <v>4307.687835915809</v>
       </c>
@@ -1519,19 +1519,19 @@
       </c>
     </row>
     <row r="21" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
       <c r="P21" s="16"/>
